--- a/reports/集团总公司_利润表_2025-04.xlsx
+++ b/reports/集团总公司_利润表_2025-04.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>220066224</v>
+        <v>238433048</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>167602139</v>
+        <v>180796243</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>627804143</v>
+        <v>679565984</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>678190</v>
+        <v>883543</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2555149</v>
+        <v>3314426</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>587118</v>
+        <v>772342</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2215153</v>
+        <v>2901987</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>499761</v>
+        <v>651045</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1876259</v>
+        <v>2450292</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>458350</v>
+        <v>599922</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1725770</v>
+        <v>2261323</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>250650</v>
+        <v>329360</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>938138</v>
+        <v>1242888</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>199909</v>
+        <v>259147</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>750934</v>
+        <v>978386</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>217392246</v>
+        <v>234937689</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164928161</v>
+        <v>177300884</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84974258</v>
+        <v>92020778</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>318294911</v>
+        <v>347409036</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1556455</v>
+        <v>2747145</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>5841645</v>
+        <v>10317580</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1400466</v>
+        <v>2000049</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5274685</v>
+        <v>7502651</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75349032</v>
+        <v>79242748</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>282047040</v>
+        <v>296425944</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1592409</v>
+        <v>2008104</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>6020203</v>
+        <v>7515058</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>701205</v>
+        <v>1004279</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2633869</v>
+        <v>3761955</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2486100</v>
+        <v>3014771</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>9400464</v>
+        <v>11300210</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1098669</v>
+        <v>1505514</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4132971</v>
+        <v>5651130</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>52294421</v>
+        <v>52175889</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>196631895</v>
+        <v>197097309</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169664</v>
+        <v>169885</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>679320</v>
+        <v>681460</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3176623</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>11981438</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2114408</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7981288</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>159062502</v>
+        <v>178957951</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>127746820</v>
+        <v>133809667</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>100744947</v>
+        <v>106670069</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>376697731</v>
+        <v>402578656</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27001873</v>
+        <v>27139598</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>101908489</v>
+        <v>101621335</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5292347</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>19877270</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1696514</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6362301</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1062117</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3979036</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1276247</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4779345</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>957906</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3588331</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>638625</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2394617</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>531821</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1997036</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2956859</v>
+        <v>2953474</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>11082711</v>
+        <v>11119240</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1383374</v>
+        <v>1393317</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5217280</v>
+        <v>5242522</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3608804</v>
+        <v>3585880</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>13527465</v>
+        <v>13541114</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>23275955</v>
+        <v>23200429</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>87558452</v>
+        <v>87561872</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>351010</v>
+        <v>2837343</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1398170</v>
+        <v>10688047</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1123054</v>
+        <v>1115581</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4478871</v>
+        <v>4474414</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1159933</v>
+        <v>1066690</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4640886</v>
+        <v>4275284</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>120597</v>
+        <v>119634</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>480414</v>
+        <v>478924</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>476418</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1903154</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>928000</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3479612</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>318701</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1269873</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>239329</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>953291</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>399146</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1590507</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1330401</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4989378</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212699</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>849779</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159307</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>637588</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>265061</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1062611</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>185219</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>743479</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132104</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>530622</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105582</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>424061</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79166</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>317712</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>58329744</v>
+        <v>59245698</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>62969504</v>
+        <v>63242837</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>529475</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1987773</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132602</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>528808</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>210456</v>
+        <v>210501</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>841108</v>
+        <v>838690</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>58119288</v>
+        <v>59564672</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7111077</v>
+        <v>7129888</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>28415115</v>
+        <v>28409400</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>51008211</v>
+        <v>52434784</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>51008211</v>
+        <v>52434784</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>51008211</v>
+        <v>52434784</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>51008211</v>
+        <v>52434784</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>51008211</v>
+        <v>52434784</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
